--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-MedicationDispense.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-MedicationDispense.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2918" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2922" uniqueCount="497">
   <si>
     <t>Property</t>
   </si>
@@ -439,7 +439,7 @@
     <t>MedicationDispense.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
@@ -496,7 +496,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -530,7 +530,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -573,7 +573,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -749,7 +749,10 @@
 </t>
   </si>
   <si>
-    <t>External identifier</t>
+    <t>An identifier intended for computation</t>
+  </si>
+  <si>
+    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
   </si>
   <si>
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
@@ -767,6 +770,9 @@
 </t>
   </si>
   <si>
+    <t>External identifier</t>
+  </si>
+  <si>
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="https://gematik.de/fhir/erp/NamingSystem/GEM_ERP_NS_PrescriptionId"/&gt;
 &lt;/valueIdentifier&gt;</t>
@@ -775,7 +781,7 @@
     <t>MedicationDispense.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Procedure|4.0.1)
+    <t xml:space="preserve">Reference(Procedure)
 </t>
   </si>
   <si>
@@ -813,6 +819,9 @@
     <t>required</t>
   </si>
   <si>
+    <t>A coded concept specifying the state of the dispense event.</t>
+  </si>
+  <si>
     <t>https://gematik.de/fhir/terminology/ValueSet/ti-medication-dispense-status-vs</t>
   </si>
   <si>
@@ -832,7 +841,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(DetectedIssue|4.0.1)</t>
+Reference(DetectedIssue)</t>
   </si>
   <si>
     <t>Why a dispense was not performed</t>
@@ -844,7 +853,7 @@
     <t>A code describing why a dispense was not performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -981,7 +990,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -992,12 +1001,6 @@
   <si>
     <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-kvid-10}
 </t>
-  </si>
-  <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
   </si>
   <si>
     <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
@@ -1030,7 +1033,7 @@
     <t>MedicationDispense.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
+    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
 </t>
   </si>
   <si>
@@ -1049,7 +1052,7 @@
     <t>MedicationDispense.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1125,7 +1128,7 @@
     <t>A code describing the role an individual played in dispensing a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function</t>
   </si>
   <si>
     <t>participation[typeCode=PRF].functionCode</t>
@@ -1162,6 +1165,9 @@
     <t>MedicationDispense.performer.actor.type</t>
   </si>
   <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+  </si>
+  <si>
     <t>MedicationDispense.performer.actor.identifier</t>
   </si>
   <si>
@@ -1169,13 +1175,19 @@
 </t>
   </si>
   <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
     <t>MedicationDispense.performer.actor.display</t>
   </si>
   <si>
     <t>MedicationDispense.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location|4.0.1)
+    <t xml:space="preserve">Reference(Location)
 </t>
   </si>
   <si>
@@ -1191,7 +1203,7 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
+    <t xml:space="preserve">Reference(MedicationRequest)
 </t>
   </si>
   <si>
@@ -1258,7 +1270,7 @@
     <t>MedicationDispense.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -1364,7 +1376,7 @@
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1)
+    <t xml:space="preserve">Reference(Patient|Practitioner)
 </t>
   </si>
   <si>
@@ -1419,6 +1431,123 @@
 The pharmacist reviews the medication order prior to dispense and updates the dosageInstruction based on the actual product being dispensed.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+DosageStructuredOrFreeTextWarning:Die Dosierungsangabe darf entweder nur als Freitext oder nur als vollständige strukturierte Information erfolgen — eine Mischung ist nicht erlaubt. {(%resource.ofType(MedicationRequest).dosageInstruction | 
+ ofType(MedicationDispense).dosageInstruction | 
+ ofType(MedicationStatement).dosage).all(
+  (text.exists() and timing.empty() and doseAndRate.empty()) or
+  (text.empty() and (timing.exists() or doseAndRate.exists()))
+)
+}DosageStructuredRequiresBoth:Wenn eine strukturierte Dosierungsangabe erfolgt, müssen sowohl timing als auch doseAndRate angegeben werden. {(%resource.ofType(MedicationRequest).dosageInstruction | 
+ ofType(MedicationDispense).dosageInstruction | 
+ ofType(MedicationStatement).dosage).all(
+  (timing.exists() implies doseAndRate.exists()) and
+  (doseAndRate.exists() implies timing.exists())
+)
+}DosageDoseUnitSameCode:Die Dosiereinheit muss über alle Dosierungen gleich sein. {(%resource.ofType(MedicationRequest).dosageInstruction | ofType(MedicationDispense).dosageInstruction | ofType(MedicationStatement).dosage).all(
+doseAndRate.exists() implies
+  (
+    %resource.dosageInstruction.doseAndRate.dose.ofType(Quantity).code | 
+    %resource.dosageInstruction.doseAndRate.dose.ofType(Range).low.code | 
+    %resource.dosageInstruction.doseAndRate.dose.ofType(Range).high.code
+  ).distinct().count() = 1
+)}DosageWarnungViererschemaInText:Hinweis: In Dosage.text wurde ein Viererschema (z. B. 1-1-1-1) erkannt. Bitte prüfen, ob dies strukturiert abgebildet werden kann. {text.exists() implies text.matches('.*\\d+\\s*[-–]\\s*\\d+\\s*[-–]\\s*\\d+\\s*[-–]\\d+.*').not()}FreeTextSingleDosageOnlyWarning:Wenn eine Dosierung als reiner Freitext angegeben ist, soll nur genau ein Dosage-Element existieren. {(
+  (%resource.ofType(MedicationRequest).dosageInstruction |
+   %resource.ofType(MedicationDispense).dosageInstruction |
+   %resource.ofType(MedicationStatement).dosage
+  ).exists(text.exists() and timing.empty() and doseAndRate.empty())
+)
+implies
+(
+  (%resource.ofType(MedicationRequest).dosageInstruction |
+   %resource.ofType(MedicationDispense).dosageInstruction |
+   %resource.ofType(MedicationStatement).dosage
+  ).count() = 1
+)}DosageStructuredOrFreeText:Die Dosierungsangabe darf entweder nur als Freitext oder nur als vollständige strukturierte Information erfolgen — eine Mischung ist nicht erlaubt. {(%resource.ofType(MedicationRequest).dosageInstruction | 
+ ofType(MedicationDispense).dosageInstruction | 
+ ofType(MedicationStatement).dosage).all(
+  (text.exists() and timing.empty() and doseAndRate.empty()) or
+  (text.empty() and (timing.exists() or doseAndRate.exists()))
+)
+}DosageStructuredRequiresGeneratedText:Liegt eine strukturierte Dosierungsangabe vor (timing und doseAndRate belegt, text leer), muss die Extension GeneratedDosageInstructionsMeta vorhanden sein. {(
+  (%resource.ofType(MedicationRequest).dosageInstruction |
+   %resource.ofType(MedicationDispense).dosageInstruction |
+   %resource.ofType(MedicationStatement).dosage
+  ).exists(timing.exists() and doseAndRate.exists() and text.empty())
+)
+implies
+(
+%resource.extension.where(
+  url = 'http://ig.fhir.de/igs/medication/StructureDefinition/GeneratedDosageInstructionsMeta'
+).exists() and
+(
+  %resource.extension.where(
+    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
+  ).exists() or
+  %resource.extension.where(
+    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
+  ).exists() or
+  %resource.extension.where(
+    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
+  ).exists()
+)
+)
+}FreeTextSingleDosageOnly:Wenn eine Dosierung als reiner Freitext angegeben ist, darf nur genau ein Dosage-Element existieren. {(
+  (%resource.ofType(MedicationRequest).dosageInstruction |
+   %resource.ofType(MedicationDispense).dosageInstruction |
+   %resource.ofType(MedicationStatement).dosage
+  ).exists(text.exists() and timing.empty() and doseAndRate.empty())
+)
+implies
+(
+  (%resource.ofType(MedicationRequest).dosageInstruction |
+   %resource.ofType(MedicationDispense).dosageInstruction |
+   %resource.ofType(MedicationStatement).dosage
+  ).count() = 1
+)}FreeTextMatchesRenderedText:Wenn eine Dosierung als reiner Freitext angegeben ist (text vorhanden, timing und doseAndRate leer) UND die Extension renderedDosageInstruction befüllt ist, muss der Wert in dosageInstruction.text mit dem Wert in der Extension übereinstimmen. {(
+  (%resource.ofType(MedicationRequest).dosageInstruction |
+   %resource.ofType(MedicationDispense).dosageInstruction |
+   %resource.ofType(MedicationStatement).dosage
+  ).where(text.exists() and timing.empty() and doseAndRate.empty()).exists()
+)
+implies
+(
+  (
+    %resource.ofType(MedicationRequest).exists() and
+    (
+      %resource.extension.where(
+        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
+      ).empty() or
+      %resource.extension.where(
+        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
+      ).value = %resource.dosageInstruction.text
+    )
+  ) or
+  (
+    %resource.ofType(MedicationDispense).exists() and
+    (
+      %resource.extension.where(
+        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
+      ).empty() or
+      %resource.extension.where(
+        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
+      ).value = %resource.dosageInstruction.text
+    )
+  ) or
+  (
+    %resource.ofType(MedicationStatement).exists() and
+    (
+      %resource.extension.where(
+        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
+      ).empty() or
+      %resource.extension.where(
+        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
+      ).value = %resource.dosage.text
+    )
+  )
+)}</t>
+  </si>
+  <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=INT]</t>
   </si>
   <si>
@@ -1507,7 +1636,7 @@
     <t>MedicationDispense.substitution.responsibleParty</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
 </t>
   </si>
   <si>
@@ -1530,7 +1659,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
+    <t xml:space="preserve">Reference(DetectedIssue)
 </t>
   </si>
   <si>
@@ -1549,7 +1678,7 @@
     <t>MedicationDispense.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance|4.0.1)
+    <t xml:space="preserve">Reference(Provenance)
 </t>
   </si>
   <si>
@@ -4045,7 +4174,7 @@
         <v>201</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4072,7 +4201,9 @@
       <c r="M19" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N19" s="2"/>
+      <c r="N19" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -4130,7 +4261,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>117</v>
@@ -4139,7 +4270,7 @@
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
@@ -4162,7 +4293,7 @@
         <v>206</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4189,7 +4320,9 @@
       <c r="M20" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="N20" s="2"/>
+      <c r="N20" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -4279,7 +4412,7 @@
         <v>211</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4306,7 +4439,9 @@
       <c r="M21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="N21" s="2"/>
+      <c r="N21" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -4364,7 +4499,7 @@
         <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>117</v>
@@ -4655,7 +4790,7 @@
         <v>234</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>224</v>
@@ -4669,7 +4804,7 @@
         <v>78</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>78</v>
@@ -4740,13 +4875,13 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>220</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>78</v>
@@ -4768,10 +4903,10 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>223</v>
@@ -4788,7 +4923,7 @@
         <v>78</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>78</v>
@@ -4859,10 +4994,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4885,16 +5020,16 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4944,7 +5079,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4956,13 +5091,13 @@
         <v>156</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4976,10 +5111,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5005,13 +5140,13 @@
         <v>173</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5019,7 +5154,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>78</v>
@@ -5037,11 +5172,13 @@
         <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -5059,7 +5196,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>88</v>
@@ -5074,16 +5211,16 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>78</v>
@@ -5091,10 +5228,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5117,13 +5254,13 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5153,10 +5290,10 @@
         <v>163</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
@@ -5174,7 +5311,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5189,10 +5326,10 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -5206,10 +5343,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5232,16 +5369,16 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5267,13 +5404,13 @@
         <v>78</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>78</v>
@@ -5291,7 +5428,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5309,7 +5446,7 @@
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5318,15 +5455,15 @@
         <v>78</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5349,16 +5486,16 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5408,7 +5545,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>88</v>
@@ -5423,27 +5560,27 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5466,16 +5603,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5525,7 +5662,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5537,30 +5674,30 @@
         <v>156</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5672,10 +5809,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5789,10 +5926,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5818,13 +5955,13 @@
         <v>102</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5874,7 +6011,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5883,7 +6020,7 @@
         <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>100</v>
@@ -5906,10 +6043,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5935,13 +6072,13 @@
         <v>130</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5970,10 +6107,10 @@
         <v>152</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>78</v>
@@ -5991,7 +6128,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6023,10 +6160,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6049,16 +6186,16 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>311</v>
+        <v>234</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>312</v>
+        <v>235</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6108,7 +6245,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6126,7 +6263,7 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6140,10 +6277,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6169,13 +6306,13 @@
         <v>102</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6225,7 +6362,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6257,10 +6394,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6283,16 +6420,16 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6342,7 +6479,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6354,13 +6491,13 @@
         <v>156</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6374,10 +6511,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6400,16 +6537,16 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6459,7 +6596,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6471,16 +6608,16 @@
         <v>156</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6491,10 +6628,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6517,13 +6654,13 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6574,7 +6711,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6589,10 +6726,10 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6606,10 +6743,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6721,10 +6858,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6838,14 +6975,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6867,10 +7004,10 @@
         <v>109</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>112</v>
@@ -6925,7 +7062,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6957,10 +7094,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6983,19 +7120,19 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7023,10 +7160,10 @@
         <v>163</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -7044,7 +7181,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7062,7 +7199,7 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7071,15 +7208,15 @@
         <v>78</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7102,16 +7239,16 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7161,7 +7298,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>88</v>
@@ -7173,13 +7310,13 @@
         <v>156</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7193,10 +7330,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7308,10 +7445,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7425,10 +7562,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7454,13 +7591,13 @@
         <v>102</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7510,7 +7647,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7519,7 +7656,7 @@
         <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>100</v>
@@ -7542,10 +7679,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7571,13 +7708,13 @@
         <v>130</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7606,10 +7743,10 @@
         <v>152</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>307</v>
+        <v>365</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -7627,7 +7764,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7659,10 +7796,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7685,16 +7822,16 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>311</v>
+        <v>368</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>312</v>
+        <v>369</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7744,7 +7881,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7753,7 +7890,7 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>100</v>
@@ -7762,7 +7899,7 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
@@ -7771,15 +7908,15 @@
         <v>78</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>78</v>
+        <v>230</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7805,13 +7942,13 @@
         <v>102</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7861,7 +7998,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7893,10 +8030,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7919,16 +8056,16 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7978,7 +8115,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7990,13 +8127,13 @@
         <v>156</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
@@ -8010,10 +8147,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8036,16 +8173,16 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8095,7 +8232,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8107,30 +8244,30 @@
         <v>156</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8242,10 +8379,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8359,10 +8496,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8388,13 +8525,13 @@
         <v>102</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8444,7 +8581,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8453,7 +8590,7 @@
         <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>100</v>
@@ -8476,10 +8613,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8505,13 +8642,13 @@
         <v>130</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8540,10 +8677,10 @@
         <v>152</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -8561,7 +8698,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8593,10 +8730,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8622,13 +8759,13 @@
         <v>221</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>311</v>
+        <v>368</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>312</v>
+        <v>369</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8678,7 +8815,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8696,7 +8833,7 @@
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8710,10 +8847,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8739,13 +8876,13 @@
         <v>102</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8795,7 +8932,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8827,10 +8964,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8853,16 +8990,16 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8891,10 +9028,10 @@
         <v>163</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -8912,7 +9049,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8930,24 +9067,24 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8970,16 +9107,16 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9029,7 +9166,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9041,30 +9178,30 @@
         <v>156</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9087,16 +9224,16 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9146,7 +9283,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9158,13 +9295,13 @@
         <v>156</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9173,15 +9310,15 @@
         <v>78</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9204,13 +9341,13 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9261,7 +9398,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9273,30 +9410,30 @@
         <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9319,13 +9456,13 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9376,42 +9513,42 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AG64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>412</v>
-      </c>
       <c r="AK64" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>415</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9434,16 +9571,16 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9493,7 +9630,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9505,30 +9642,30 @@
         <v>156</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9551,16 +9688,16 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9610,7 +9747,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9622,19 +9759,19 @@
         <v>156</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -9642,10 +9779,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9668,16 +9805,16 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9727,7 +9864,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9742,10 +9879,10 @@
         <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -9754,15 +9891,15 @@
         <v>78</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9785,16 +9922,16 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9844,7 +9981,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9853,16 +9990,16 @@
         <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>100</v>
+        <v>449</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>78</v>
@@ -9876,10 +10013,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9902,13 +10039,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9959,7 +10096,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9977,13 +10114,13 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -9991,10 +10128,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10106,10 +10243,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10223,14 +10360,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10252,10 +10389,10 @@
         <v>109</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>112</v>
@@ -10310,7 +10447,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10342,10 +10479,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10368,13 +10505,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10425,7 +10562,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>88</v>
@@ -10443,7 +10580,7 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10457,10 +10594,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10483,16 +10620,16 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10521,10 +10658,10 @@
         <v>163</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>78</v>
@@ -10542,7 +10679,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10560,24 +10697,24 @@
         <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10600,16 +10737,16 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10638,10 +10775,10 @@
         <v>163</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>78</v>
@@ -10659,7 +10796,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10677,24 +10814,24 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10717,16 +10854,16 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10776,7 +10913,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10788,19 +10925,19 @@
         <v>156</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -10808,14 +10945,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10834,16 +10971,16 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10893,7 +11030,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10905,13 +11042,13 @@
         <v>156</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>78</v>
@@ -10925,10 +11062,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10951,16 +11088,16 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11010,7 +11147,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11022,13 +11159,13 @@
         <v>156</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>78</v>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-MedicationDispense.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-MedicationDispense.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2922" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2918" uniqueCount="492">
   <si>
     <t>Property</t>
   </si>
@@ -439,7 +439,7 @@
     <t>MedicationDispense.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -496,7 +496,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -530,7 +530,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -573,7 +573,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -749,10 +749,7 @@
 </t>
   </si>
   <si>
-    <t>An identifier intended for computation</t>
-  </si>
-  <si>
-    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
+    <t>External identifier</t>
   </si>
   <si>
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
@@ -770,9 +767,6 @@
 </t>
   </si>
   <si>
-    <t>External identifier</t>
-  </si>
-  <si>
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="https://gematik.de/fhir/erp/NamingSystem/GEM_ERP_NS_PrescriptionId"/&gt;
 &lt;/valueIdentifier&gt;</t>
@@ -781,7 +775,7 @@
     <t>MedicationDispense.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Procedure)
+    <t xml:space="preserve">Reference(Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -819,9 +813,6 @@
     <t>required</t>
   </si>
   <si>
-    <t>A coded concept specifying the state of the dispense event.</t>
-  </si>
-  <si>
     <t>https://gematik.de/fhir/terminology/ValueSet/ti-medication-dispense-status-vs</t>
   </si>
   <si>
@@ -841,7 +832,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(DetectedIssue)</t>
+Reference(DetectedIssue|4.0.1)</t>
   </si>
   <si>
     <t>Why a dispense was not performed</t>
@@ -853,7 +844,7 @@
     <t>A code describing why a dispense was not performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -990,7 +981,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1001,6 +992,12 @@
   <si>
     <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-kvid-10}
 </t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
   </si>
   <si>
     <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
@@ -1033,7 +1030,7 @@
     <t>MedicationDispense.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1052,7 +1049,7 @@
     <t>MedicationDispense.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1128,7 +1125,7 @@
     <t>A code describing the role an individual played in dispensing a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function|4.0.1</t>
   </si>
   <si>
     <t>participation[typeCode=PRF].functionCode</t>
@@ -1165,9 +1162,6 @@
     <t>MedicationDispense.performer.actor.type</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
-  </si>
-  <si>
     <t>MedicationDispense.performer.actor.identifier</t>
   </si>
   <si>
@@ -1175,19 +1169,13 @@
 </t>
   </si>
   <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
-  </si>
-  <si>
     <t>MedicationDispense.performer.actor.display</t>
   </si>
   <si>
     <t>MedicationDispense.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1203,7 +1191,7 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1270,7 +1258,7 @@
     <t>MedicationDispense.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1376,7 +1364,7 @@
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1)
 </t>
   </si>
   <si>
@@ -1431,123 +1419,6 @@
 The pharmacist reviews the medication order prior to dispense and updates the dosageInstruction based on the actual product being dispensed.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-DosageStructuredOrFreeTextWarning:Die Dosierungsangabe darf entweder nur als Freitext oder nur als vollständige strukturierte Information erfolgen — eine Mischung ist nicht erlaubt. {(%resource.ofType(MedicationRequest).dosageInstruction | 
- ofType(MedicationDispense).dosageInstruction | 
- ofType(MedicationStatement).dosage).all(
-  (text.exists() and timing.empty() and doseAndRate.empty()) or
-  (text.empty() and (timing.exists() or doseAndRate.exists()))
-)
-}DosageStructuredRequiresBoth:Wenn eine strukturierte Dosierungsangabe erfolgt, müssen sowohl timing als auch doseAndRate angegeben werden. {(%resource.ofType(MedicationRequest).dosageInstruction | 
- ofType(MedicationDispense).dosageInstruction | 
- ofType(MedicationStatement).dosage).all(
-  (timing.exists() implies doseAndRate.exists()) and
-  (doseAndRate.exists() implies timing.exists())
-)
-}DosageDoseUnitSameCode:Die Dosiereinheit muss über alle Dosierungen gleich sein. {(%resource.ofType(MedicationRequest).dosageInstruction | ofType(MedicationDispense).dosageInstruction | ofType(MedicationStatement).dosage).all(
-doseAndRate.exists() implies
-  (
-    %resource.dosageInstruction.doseAndRate.dose.ofType(Quantity).code | 
-    %resource.dosageInstruction.doseAndRate.dose.ofType(Range).low.code | 
-    %resource.dosageInstruction.doseAndRate.dose.ofType(Range).high.code
-  ).distinct().count() = 1
-)}DosageWarnungViererschemaInText:Hinweis: In Dosage.text wurde ein Viererschema (z. B. 1-1-1-1) erkannt. Bitte prüfen, ob dies strukturiert abgebildet werden kann. {text.exists() implies text.matches('.*\\d+\\s*[-–]\\s*\\d+\\s*[-–]\\s*\\d+\\s*[-–]\\d+.*').not()}FreeTextSingleDosageOnlyWarning:Wenn eine Dosierung als reiner Freitext angegeben ist, soll nur genau ein Dosage-Element existieren. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).exists(text.exists() and timing.empty() and doseAndRate.empty())
-)
-implies
-(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).count() = 1
-)}DosageStructuredOrFreeText:Die Dosierungsangabe darf entweder nur als Freitext oder nur als vollständige strukturierte Information erfolgen — eine Mischung ist nicht erlaubt. {(%resource.ofType(MedicationRequest).dosageInstruction | 
- ofType(MedicationDispense).dosageInstruction | 
- ofType(MedicationStatement).dosage).all(
-  (text.exists() and timing.empty() and doseAndRate.empty()) or
-  (text.empty() and (timing.exists() or doseAndRate.exists()))
-)
-}DosageStructuredRequiresGeneratedText:Liegt eine strukturierte Dosierungsangabe vor (timing und doseAndRate belegt, text leer), muss die Extension GeneratedDosageInstructionsMeta vorhanden sein. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).exists(timing.exists() and doseAndRate.exists() and text.empty())
-)
-implies
-(
-%resource.extension.where(
-  url = 'http://ig.fhir.de/igs/medication/StructureDefinition/GeneratedDosageInstructionsMeta'
-).exists() and
-(
-  %resource.extension.where(
-    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
-  ).exists() or
-  %resource.extension.where(
-    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
-  ).exists() or
-  %resource.extension.where(
-    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
-  ).exists()
-)
-)
-}FreeTextSingleDosageOnly:Wenn eine Dosierung als reiner Freitext angegeben ist, darf nur genau ein Dosage-Element existieren. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).exists(text.exists() and timing.empty() and doseAndRate.empty())
-)
-implies
-(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).count() = 1
-)}FreeTextMatchesRenderedText:Wenn eine Dosierung als reiner Freitext angegeben ist (text vorhanden, timing und doseAndRate leer) UND die Extension renderedDosageInstruction befüllt ist, muss der Wert in dosageInstruction.text mit dem Wert in der Extension übereinstimmen. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).where(text.exists() and timing.empty() and doseAndRate.empty()).exists()
-)
-implies
-(
-  (
-    %resource.ofType(MedicationRequest).exists() and
-    (
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
-      ).empty() or
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
-      ).value = %resource.dosageInstruction.text
-    )
-  ) or
-  (
-    %resource.ofType(MedicationDispense).exists() and
-    (
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
-      ).empty() or
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
-      ).value = %resource.dosageInstruction.text
-    )
-  ) or
-  (
-    %resource.ofType(MedicationStatement).exists() and
-    (
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
-      ).empty() or
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
-      ).value = %resource.dosage.text
-    )
-  )
-)}</t>
-  </si>
-  <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=INT]</t>
   </si>
   <si>
@@ -1636,7 +1507,7 @@
     <t>MedicationDispense.substitution.responsibleParty</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1659,7 +1530,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -1678,7 +1549,7 @@
     <t>MedicationDispense.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -4174,7 +4045,7 @@
         <v>201</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4201,9 +4072,7 @@
       <c r="M19" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N19" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -4261,7 +4130,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>117</v>
@@ -4270,7 +4139,7 @@
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>196</v>
+        <v>78</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
@@ -4293,7 +4162,7 @@
         <v>206</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4320,9 +4189,7 @@
       <c r="M20" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="N20" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -4412,7 +4279,7 @@
         <v>211</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4439,9 +4306,7 @@
       <c r="M21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="N21" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -4499,7 +4364,7 @@
         <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>117</v>
@@ -4790,7 +4655,7 @@
         <v>234</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>224</v>
@@ -4804,7 +4669,7 @@
         <v>78</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>78</v>
@@ -4875,13 +4740,13 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>220</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>78</v>
@@ -4903,10 +4768,10 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>223</v>
@@ -4923,7 +4788,7 @@
         <v>78</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>78</v>
@@ -4994,10 +4859,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5020,16 +4885,16 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5079,7 +4944,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5091,13 +4956,13 @@
         <v>156</v>
       </c>
       <c r="AJ26" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -5111,10 +4976,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5140,13 +5005,13 @@
         <v>173</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5154,7 +5019,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>78</v>
@@ -5172,13 +5037,11 @@
         <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -5196,7 +5059,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>88</v>
@@ -5211,16 +5074,16 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>78</v>
@@ -5228,10 +5091,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5254,13 +5117,13 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5290,10 +5153,10 @@
         <v>163</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
@@ -5311,7 +5174,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5326,10 +5189,10 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -5343,10 +5206,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5369,16 +5232,16 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5404,13 +5267,13 @@
         <v>78</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>78</v>
@@ -5428,7 +5291,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5446,7 +5309,7 @@
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5455,15 +5318,15 @@
         <v>78</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5486,16 +5349,16 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5545,7 +5408,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>88</v>
@@ -5560,27 +5423,27 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5603,16 +5466,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5662,7 +5525,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5674,30 +5537,30 @@
         <v>156</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>296</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5809,10 +5672,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5926,10 +5789,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5955,13 +5818,13 @@
         <v>102</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6011,7 +5874,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6020,7 +5883,7 @@
         <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>100</v>
@@ -6043,10 +5906,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6072,13 +5935,13 @@
         <v>130</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6107,10 +5970,10 @@
         <v>152</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>78</v>
@@ -6128,7 +5991,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6160,10 +6023,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6186,16 +6049,16 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6245,7 +6108,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6263,7 +6126,7 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6277,10 +6140,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6306,13 +6169,13 @@
         <v>102</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6362,7 +6225,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6394,10 +6257,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6420,16 +6283,16 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M38" t="s" s="2">
-        <v>325</v>
-      </c>
       <c r="N38" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6479,7 +6342,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6491,13 +6354,13 @@
         <v>156</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6511,10 +6374,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6537,16 +6400,16 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M39" t="s" s="2">
-        <v>331</v>
-      </c>
       <c r="N39" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6596,7 +6459,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6608,16 +6471,16 @@
         <v>156</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6628,10 +6491,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6654,13 +6517,13 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6711,7 +6574,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6726,10 +6589,10 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6743,10 +6606,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6858,10 +6721,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6975,14 +6838,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7004,10 +6867,10 @@
         <v>109</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>112</v>
@@ -7062,7 +6925,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7094,10 +6957,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7120,19 +6983,19 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7160,11 +7023,11 @@
         <v>163</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>353</v>
-      </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
       </c>
@@ -7181,7 +7044,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7199,7 +7062,7 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7208,15 +7071,15 @@
         <v>78</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7239,16 +7102,16 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="M45" t="s" s="2">
-        <v>358</v>
-      </c>
       <c r="N45" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7298,7 +7161,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>88</v>
@@ -7310,13 +7173,13 @@
         <v>156</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7330,10 +7193,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7445,10 +7308,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7562,10 +7425,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7591,13 +7454,13 @@
         <v>102</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7647,7 +7510,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7656,7 +7519,7 @@
         <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>100</v>
@@ -7679,10 +7542,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7708,13 +7571,13 @@
         <v>130</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7743,10 +7606,10 @@
         <v>152</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>365</v>
+        <v>307</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -7764,7 +7627,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7796,10 +7659,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7822,16 +7685,16 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>368</v>
+        <v>311</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>369</v>
+        <v>312</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7881,7 +7744,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7890,7 +7753,7 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>100</v>
@@ -7899,7 +7762,7 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
@@ -7908,15 +7771,15 @@
         <v>78</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>230</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7942,13 +7805,13 @@
         <v>102</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7998,7 +7861,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8030,10 +7893,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8056,16 +7919,16 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8115,7 +7978,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8127,13 +7990,13 @@
         <v>156</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
@@ -8147,10 +8010,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8173,16 +8036,16 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8232,7 +8095,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8244,30 +8107,30 @@
         <v>156</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8379,10 +8242,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8496,10 +8359,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8525,13 +8388,13 @@
         <v>102</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8581,7 +8444,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8590,7 +8453,7 @@
         <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>100</v>
@@ -8613,10 +8476,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8642,13 +8505,13 @@
         <v>130</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8677,10 +8540,10 @@
         <v>152</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -8698,7 +8561,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8730,10 +8593,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8759,13 +8622,13 @@
         <v>221</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>368</v>
+        <v>311</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>369</v>
+        <v>312</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8815,7 +8678,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8833,7 +8696,7 @@
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8847,10 +8710,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8876,13 +8739,13 @@
         <v>102</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8932,7 +8795,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8964,10 +8827,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8990,16 +8853,16 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9028,10 +8891,10 @@
         <v>163</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -9049,7 +8912,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9067,24 +8930,24 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9107,16 +8970,16 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9166,7 +9029,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9178,30 +9041,30 @@
         <v>156</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9224,16 +9087,16 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9283,7 +9146,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9295,13 +9158,13 @@
         <v>156</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9310,15 +9173,15 @@
         <v>78</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9341,13 +9204,13 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9398,42 +9261,42 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AG63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>416</v>
-      </c>
       <c r="AK63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9456,13 +9319,13 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9513,42 +9376,42 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AG64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>424</v>
-      </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9571,16 +9434,16 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9630,7 +9493,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9642,30 +9505,30 @@
         <v>156</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9688,16 +9551,16 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9747,7 +9610,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9759,19 +9622,19 @@
         <v>156</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -9779,10 +9642,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9805,16 +9668,16 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9864,7 +9727,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9879,10 +9742,10 @@
         <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -9891,15 +9754,15 @@
         <v>78</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9922,16 +9785,16 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9981,7 +9844,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9990,16 +9853,16 @@
         <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>449</v>
+        <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>78</v>
@@ -10013,10 +9876,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10039,13 +9902,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10096,7 +9959,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10114,13 +9977,13 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -10128,10 +9991,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10243,10 +10106,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10360,14 +10223,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10389,10 +10252,10 @@
         <v>109</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>112</v>
@@ -10447,7 +10310,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10479,10 +10342,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10505,13 +10368,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10562,7 +10425,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>88</v>
@@ -10580,7 +10443,7 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10594,10 +10457,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10620,16 +10483,16 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10658,10 +10521,10 @@
         <v>163</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>78</v>
@@ -10679,7 +10542,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10697,24 +10560,24 @@
         <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10737,16 +10600,16 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10775,10 +10638,10 @@
         <v>163</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>78</v>
@@ -10796,7 +10659,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10814,24 +10677,24 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10854,16 +10717,16 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10913,7 +10776,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10925,19 +10788,19 @@
         <v>156</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -10945,14 +10808,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10971,16 +10834,16 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11030,7 +10893,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11042,13 +10905,13 @@
         <v>156</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>78</v>
@@ -11062,10 +10925,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11088,16 +10951,16 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11147,7 +11010,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11159,13 +11022,13 @@
         <v>156</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>78</v>
